--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3970,7 +3970,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4374,7 +4374,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>166</v>
       </c>
@@ -4389,13 +4389,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4477,7 +4477,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>170</v>
       </c>
@@ -4492,13 +4492,13 @@
         <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4786,7 +4786,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>184</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
